--- a/data/data100+1000000.xlsx
+++ b/data/data100+1000000.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatsOeynhausen\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MatsOeynhausen\Desktop\algorithms\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A472B752-9829-451E-AA5B-0ED49BFE2FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C941725A-8193-4442-BA93-EBC2315DF56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A368FE0E-F61E-4BFE-8BD8-E8D291B96482}"/>
   </bookViews>
@@ -85,28 +85,28 @@
     <t>Shellsort</t>
   </si>
   <si>
-    <t>Selectionsort2</t>
+    <t>Bubblesort</t>
   </si>
   <si>
-    <t>Radixsort2</t>
+    <t>Countsort</t>
   </si>
   <si>
-    <t>Quicksort2</t>
+    <t>Heapsort</t>
   </si>
   <si>
-    <t>Mergesort2</t>
+    <t>Insertionsort</t>
   </si>
   <si>
-    <t>Insertionsort2</t>
+    <t>Mergesort</t>
   </si>
   <si>
-    <t>Heapsort2</t>
+    <t>Quicksort</t>
   </si>
   <si>
-    <t>Countsort2</t>
+    <t>Radixsort</t>
   </si>
   <si>
-    <t>Bubblesort2</t>
+    <t>Selectionsort</t>
   </si>
 </sst>
 </file>
@@ -693,7 +693,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -912,7 +912,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1179,7 +1179,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1428,7 +1428,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="FFFF00"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1656,7 +1656,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:srgbClr val="92D050"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1911,7 +1911,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:srgbClr val="00B050"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2163,9 +2163,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2420,9 +2418,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2647,9 +2643,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:srgbClr val="002060"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2917,6 +2911,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Arraylänge</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2965,7 +3014,7 @@
         <c:axId val="328108783"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="6"/>
+          <c:max val="0.5"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2983,6 +3032,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Zeit in Sekunden</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3129,7 +3233,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bubblesort2</c:v>
+                  <c:v>Bubblesort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3348,7 +3452,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Countsort2</c:v>
+                  <c:v>Countsort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3615,7 +3719,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Heapsort2</c:v>
+                  <c:v>Heapsort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3861,7 +3965,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Insertionsort2</c:v>
+                  <c:v>Insertionsort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4080,7 +4184,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Mergesort2</c:v>
+                  <c:v>Mergesort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4332,7 +4436,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Quicksort2</c:v>
+                  <c:v>Quicksort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4581,7 +4685,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Radixsort2</c:v>
+                  <c:v>Radixsort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4836,7 +4940,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Selectionsort2</c:v>
+                  <c:v>Selectionsort</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5331,6 +5435,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Arraylänge</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -5379,6 +5538,7 @@
         <c:axId val="317766399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -5396,6 +5556,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Geschwindigkeits</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Faktor</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -5550,7 +5770,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5561,10 +5781,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'data100+1000000'!$A$2:$A$15</c:f>
+              <c:f>'data100+1000000'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -5606,16 +5826,28 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data100+1000000'!$B$2:$B$15</c:f>
+              <c:f>'data100+1000000'!$B$2:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>3.0000000000000001E-6</c:v>
                 </c:pt>
@@ -5657,6 +5889,18 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>5.22E-4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.3999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.0605E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.3068E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.2049000000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5685,7 +5929,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5696,10 +5940,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'data100+1000000'!$A$2:$A$15</c:f>
+              <c:f>'data100+1000000'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -5741,16 +5985,28 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data100+1000000'!$C$2:$C$15</c:f>
+              <c:f>'data100+1000000'!$C$2:$C$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5792,6 +6048,18 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>3.0000000000000001E-6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.0000000000000004E-6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.0000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.5E-5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.0999999999999999E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5820,7 +6088,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="FFC000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5831,10 +6099,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'data100+1000000'!$A$2:$A$15</c:f>
+              <c:f>'data100+1000000'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -5876,16 +6144,28 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data100+1000000'!$D$2:$D$15</c:f>
+              <c:f>'data100+1000000'!$D$2:$D$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5927,6 +6207,18 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>5.3000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.5300000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.1100000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.3900000000000003E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5955,7 +6247,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="FFFF00"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5966,10 +6258,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'data100+1000000'!$A$2:$A$15</c:f>
+              <c:f>'data100+1000000'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -6011,16 +6303,28 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data100+1000000'!$E$2:$E$15</c:f>
+              <c:f>'data100+1000000'!$E$2:$E$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6062,6 +6366,18 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>4.0000000000000003E-5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.22E-4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.5400000000000005E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.885E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.3149999999999998E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6090,7 +6406,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent5"/>
+                <a:srgbClr val="92D050"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6101,10 +6417,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'data100+1000000'!$A$2:$A$15</c:f>
+              <c:f>'data100+1000000'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -6146,16 +6462,28 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data100+1000000'!$F$2:$F$15</c:f>
+              <c:f>'data100+1000000'!$F$2:$F$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6197,6 +6525,18 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>4.0000000000000003E-5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.05E-4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.14E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.2499999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.1800000000000002E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6225,7 +6565,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent6"/>
+                <a:srgbClr val="00B050"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6236,10 +6576,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'data100+1000000'!$A$2:$A$15</c:f>
+              <c:f>'data100+1000000'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -6281,16 +6621,28 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data100+1000000'!$G$2:$G$15</c:f>
+              <c:f>'data100+1000000'!$G$2:$G$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6332,6 +6684,18 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>3.6999999999999998E-5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.8999999999999995E-5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.7200000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.5000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.3599999999999998E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6360,9 +6724,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:srgbClr val="00B0F0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6373,10 +6735,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'data100+1000000'!$A$2:$A$15</c:f>
+              <c:f>'data100+1000000'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -6418,16 +6780,28 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data100+1000000'!$H$2:$H$15</c:f>
+              <c:f>'data100+1000000'!$H$2:$H$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6469,6 +6843,18 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1.0000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.9E-5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.8000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.8999999999999997E-5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9.2E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6497,9 +6883,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6510,10 +6894,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'data100+1000000'!$A$2:$A$15</c:f>
+              <c:f>'data100+1000000'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -6555,16 +6939,28 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data100+1000000'!$I$2:$I$15</c:f>
+              <c:f>'data100+1000000'!$I$2:$I$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6606,6 +7002,18 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1.75E-4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.9500000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.9119999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.4799999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.5011999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6634,9 +7042,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
+                <a:srgbClr val="002060"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6647,10 +7053,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'data100+1000000'!$A$2:$A$15</c:f>
+              <c:f>'data100+1000000'!$A$2:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -6692,16 +7098,28 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'data100+1000000'!$J$2:$J$15</c:f>
+              <c:f>'data100+1000000'!$J$2:$J$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6743,6 +7161,18 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>3.6999999999999998E-5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.05E-4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.2599999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.5E-4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4.8299999999999998E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6787,6 +7217,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Arraylänge</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -6852,6 +7337,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Zeit in Sekunden</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -8644,13 +9184,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>388056</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>148324</xdr:rowOff>
+      <xdr:rowOff>148323</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>924685</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>101829</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>57188</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>44049</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8678,15 +9218,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>240393</xdr:colOff>
+      <xdr:colOff>240392</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>133349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>55</xdr:col>
-      <xdr:colOff>129722</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>9978</xdr:rowOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>360708</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>29075</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8716,13 +9256,13 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>275724</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>100264</xdr:rowOff>
+      <xdr:rowOff>100263</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>247311</xdr:colOff>
+      <xdr:colOff>237624</xdr:colOff>
       <xdr:row>83</xdr:row>
-      <xdr:rowOff>53769</xdr:rowOff>
+      <xdr:rowOff>176463</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8795,14 +9335,14 @@
   <autoFilter ref="U1:AD37" xr:uid="{9A983B2F-17B5-42C2-9E7A-13C80F54AD57}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{326AC32D-50F6-4F19-8A18-F54EBD78C101}" name="Column2"/>
-    <tableColumn id="2" xr3:uid="{64B1693C-5F37-4B95-9904-9B317FD528C2}" name="Bubblesort2"/>
-    <tableColumn id="3" xr3:uid="{1AF92B55-EDCF-4406-93A4-F891DA4506B5}" name="Countsort2"/>
-    <tableColumn id="4" xr3:uid="{4ED7C344-9FCE-4968-BD57-09E68F6936D6}" name="Heapsort2"/>
-    <tableColumn id="5" xr3:uid="{5FB196ED-FEC9-4AA2-A588-DE7662BEE86A}" name="Insertionsort2"/>
-    <tableColumn id="6" xr3:uid="{5514C4B2-6D26-4070-85E0-42CDD21A7C34}" name="Mergesort2"/>
-    <tableColumn id="7" xr3:uid="{0A7F671E-285A-46D4-B356-C3856B796978}" name="Quicksort2"/>
-    <tableColumn id="8" xr3:uid="{3A9CCC3C-3032-44FB-A4B0-330BDE9D6DD1}" name="Radixsort2"/>
-    <tableColumn id="9" xr3:uid="{B9EF1D82-EBF8-4761-A287-2D1D5B7886BA}" name="Selectionsort2"/>
+    <tableColumn id="2" xr3:uid="{64B1693C-5F37-4B95-9904-9B317FD528C2}" name="Bubblesort"/>
+    <tableColumn id="3" xr3:uid="{1AF92B55-EDCF-4406-93A4-F891DA4506B5}" name="Countsort"/>
+    <tableColumn id="4" xr3:uid="{4ED7C344-9FCE-4968-BD57-09E68F6936D6}" name="Heapsort"/>
+    <tableColumn id="5" xr3:uid="{5FB196ED-FEC9-4AA2-A588-DE7662BEE86A}" name="Insertionsort"/>
+    <tableColumn id="6" xr3:uid="{5514C4B2-6D26-4070-85E0-42CDD21A7C34}" name="Mergesort"/>
+    <tableColumn id="7" xr3:uid="{0A7F671E-285A-46D4-B356-C3856B796978}" name="Quicksort"/>
+    <tableColumn id="8" xr3:uid="{3A9CCC3C-3032-44FB-A4B0-330BDE9D6DD1}" name="Radixsort"/>
+    <tableColumn id="9" xr3:uid="{B9EF1D82-EBF8-4761-A287-2D1D5B7886BA}" name="Selectionsort"/>
     <tableColumn id="10" xr3:uid="{B475D481-16CF-4DCE-BB64-7C174188DC9A}" name="Shellsort"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -9219,28 +9759,28 @@
         <v>19</v>
       </c>
       <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
         <v>28</v>
-      </c>
-      <c r="W1" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>21</v>
       </c>
       <c r="AD1" t="s">
         <v>20</v>
